--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-06-2025.xlsx
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
